--- a/data/trans_orig/P25C_R2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P25C_R2_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos) en 2023</t>
+          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos) en 2023 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10257</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,77 +745,77 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,25%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3080</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>6,95%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>6558</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>11447</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>1,74%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3044</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,87%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>6558</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>3339</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>11452</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>155482</t>
+          <t>155379</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>162852</t>
+          <t>162929</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,82 +858,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>98,3%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>43746</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>41259</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>44339</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>98,66%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>93,05%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>203520</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>198631</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>206413</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>94,55%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>98,26%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>43746</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>41295</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>44339</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,66%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>93,13%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>203520</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>198626</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>206739</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>96,88%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>94,55%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14872</t>
+          <t>14852</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13882</t>
+          <t>14041</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26643</t>
+          <t>26333</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>529535</t>
+          <t>529555</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>543802</t>
+          <t>543388</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>189242</t>
+          <t>189083</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>198125</t>
+          <t>198037</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>720888</t>
+          <t>721198</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>741788</t>
+          <t>742130</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>566</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2693</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>11443</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>131889</t>
+          <t>131921</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>136748</t>
+          <t>136769</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78812</t>
+          <t>78489</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85801</t>
+          <t>85657</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>213428</t>
+          <t>212984</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>221734</t>
+          <t>221660</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23743</t>
+          <t>23694</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8321</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19413</t>
+          <t>20084</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13531</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39745</t>
+          <t>38824</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>823738</t>
+          <t>823787</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>842585</t>
+          <t>841963</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>315142</t>
+          <t>314471</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>326197</t>
+          <t>326234</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1142292</t>
+          <t>1143213</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1168506</t>
+          <t>1169540</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25C_R2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P25C_R2_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>12026</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>609</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>12299</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>159774</t>
+          <t>169540</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>155379</t>
+          <t>164093</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>162929</t>
+          <t>172834</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>43746</t>
+          <t>46443</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41259</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44339</t>
+          <t>47052</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>203520</t>
+          <t>215983</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>198631</t>
+          <t>210872</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>206413</t>
+          <t>219549</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>165739</t>
+          <t>176119</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>165739</t>
+          <t>176119</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>165739</t>
+          <t>176119</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>44339</t>
+          <t>47052</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44339</t>
+          <t>47052</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44339</t>
+          <t>47052</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>210078</t>
+          <t>223171</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>210078</t>
+          <t>223171</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>210078</t>
+          <t>223171</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>12401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,22 +1103,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>9398</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>5561</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14041</t>
+          <t>14966</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15786</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>9867</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26333</t>
+          <t>24872</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>538220</t>
+          <t>326103</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>529555</t>
+          <t>320089</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>543388</t>
+          <t>329905</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,27 +1216,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>194262</t>
+          <t>212725</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>189083</t>
+          <t>207157</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>198037</t>
+          <t>216562</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>732481</t>
+          <t>538827</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>721198</t>
+          <t>529741</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>742130</t>
+          <t>544746</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>544407</t>
+          <t>332490</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>544407</t>
+          <t>332490</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>544407</t>
+          <t>332490</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>203124</t>
+          <t>222123</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>203124</t>
+          <t>222123</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>203124</t>
+          <t>222123</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>747531</t>
+          <t>554613</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>747531</t>
+          <t>554613</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>747531</t>
+          <t>554613</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>585</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8603</t>
+          <t>9828</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>6487</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11443</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>135324</t>
+          <t>146723</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>131921</t>
+          <t>143518</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>136769</t>
+          <t>148102</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>83324</t>
+          <t>91065</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78489</t>
+          <t>85761</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85657</t>
+          <t>94072</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>218649</t>
+          <t>237790</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>212984</t>
+          <t>232411</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>221660</t>
+          <t>240988</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>137335</t>
+          <t>148687</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>137335</t>
+          <t>148687</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>137335</t>
+          <t>148687</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>87092</t>
+          <t>95589</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>87092</t>
+          <t>95589</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87092</t>
+          <t>95589</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>224427</t>
+          <t>244277</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>224427</t>
+          <t>244277</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>224427</t>
+          <t>244277</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>14930</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23694</t>
+          <t>22125</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8321</t>
+          <t>9639</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20084</t>
+          <t>21906</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>29461</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>21707</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38824</t>
+          <t>40435</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>833318</t>
+          <t>642367</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>823787</t>
+          <t>635172</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>841963</t>
+          <t>648401</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>321332</t>
+          <t>350233</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>314471</t>
+          <t>342858</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>326234</t>
+          <t>355125</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1154651</t>
+          <t>992600</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1143213</t>
+          <t>981626</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1169540</t>
+          <t>1000354</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>847481</t>
+          <t>657297</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>847481</t>
+          <t>657297</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>847481</t>
+          <t>657297</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>334555</t>
+          <t>364764</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>334555</t>
+          <t>364764</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>334555</t>
+          <t>364764</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1182037</t>
+          <t>1022061</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1182037</t>
+          <t>1022061</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1182037</t>
+          <t>1022061</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
